--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_28_8.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_28_8.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_0</t>
+          <t>model_28_8_24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9994513843903431</v>
+        <v>0.99977785879728</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5177225822059734</v>
+        <v>0.6773041904928438</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9987842409027156</v>
+        <v>0.9995591441310874</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9989673644957774</v>
+        <v>0.9990754909931069</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9988613357274077</v>
+        <v>0.9992002900751297</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003256819248526732</v>
+        <v>0.000131872613934875</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2863007085022101</v>
+        <v>0.1915661722565882</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007294391527873815</v>
+        <v>8.702780522085726e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000347270941627246</v>
+        <v>0.0006916947183605441</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0005383550472073138</v>
+        <v>0.0003893612617907007</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01103831738361292</v>
+        <v>0.003809713657361903</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01804665965913562</v>
+        <v>0.01148358018802825</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000387258077405</v>
+        <v>1.000156805554861</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01881494332256057</v>
+        <v>0.01197245997092071</v>
       </c>
       <c r="P2" t="n">
-        <v>132.059178687059</v>
+        <v>133.8673482945649</v>
       </c>
       <c r="Q2" t="n">
-        <v>202.7539765294146</v>
+        <v>204.5621461369205</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_1</t>
+          <t>model_28_8_23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9994634769274753</v>
+        <v>0.9997855777571463</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5173300171468627</v>
+        <v>0.677143701980623</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9987341584358905</v>
+        <v>0.9995765442656956</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9989121152665691</v>
+        <v>0.9991157418009905</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9988099069529103</v>
+        <v>0.9992347448330453</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0003185032724405919</v>
+        <v>0.0001272903059165394</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2865337520792259</v>
+        <v>0.1916614451701852</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007594879611836779</v>
+        <v>8.359290589823846e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003658510231496483</v>
+        <v>0.0006615800618074545</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005626703269511017</v>
+        <v>0.0003725859941599065</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01075178321471145</v>
+        <v>0.003796896129233266</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01784665997996801</v>
+        <v>0.01128230055957292</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000378722168841</v>
+        <v>1.000151356877309</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01860642924299438</v>
+        <v>0.01176261145197577</v>
       </c>
       <c r="P3" t="n">
-        <v>132.1037556169322</v>
+        <v>133.9380804135621</v>
       </c>
       <c r="Q3" t="n">
-        <v>202.7985534592878</v>
+        <v>204.6328782559177</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_2</t>
+          <t>model_28_8_22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9994734474286804</v>
+        <v>0.9997934237159413</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5169569569041987</v>
+        <v>0.6769743348703354</v>
       </c>
       <c r="D4" t="n">
-        <v>0.998685502595781</v>
+        <v>0.9995944730852927</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9988580092370648</v>
+        <v>0.9991572003664843</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9987597934933139</v>
+        <v>0.9992702327256801</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003125843522220147</v>
+        <v>0.0001226326058480755</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2867552167546346</v>
+        <v>0.1917619888031302</v>
       </c>
       <c r="I4" t="n">
-        <v>0.000788680812684377</v>
+        <v>8.005364073299555e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0003840466514587846</v>
+        <v>0.0006305617909533667</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0005863637320715808</v>
+        <v>0.0003553077158431811</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0104795090177348</v>
+        <v>0.003783399240491717</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0176800552098124</v>
+        <v>0.01107396071187159</v>
       </c>
       <c r="N4" t="n">
-        <v>1.00037168416799</v>
+        <v>1.000145818553453</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01843273176285383</v>
+        <v>0.01154540214563485</v>
       </c>
       <c r="P4" t="n">
-        <v>132.1412723962023</v>
+        <v>134.0126352334752</v>
       </c>
       <c r="Q4" t="n">
-        <v>202.8360702385579</v>
+        <v>204.7074330758308</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_3</t>
+          <t>model_28_8_21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9994815637805379</v>
+        <v>0.999801365878933</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5166025667590214</v>
+        <v>0.6767957293441864</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9986383749897977</v>
+        <v>0.9996129388428776</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9988051658327749</v>
+        <v>0.9991997758969863</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9987110969958662</v>
+        <v>0.9993066886839554</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000307766135151298</v>
+        <v>0.0001179177948126261</v>
       </c>
       <c r="H5" t="n">
-        <v>0.286965598053669</v>
+        <v>0.1918680167588092</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0008169567442058418</v>
+        <v>7.640838052965223e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004018176642619358</v>
+        <v>0.0005987078345721471</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0006093872042338888</v>
+        <v>0.0003375581075508997</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01022076913029834</v>
+        <v>0.003769123250210362</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01754326466628427</v>
+        <v>0.01085899603152271</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000365954978444</v>
+        <v>1.000140212320753</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01829011776269223</v>
+        <v>0.0113212859738053</v>
       </c>
       <c r="P5" t="n">
-        <v>132.1723407297258</v>
+        <v>134.0910456608103</v>
       </c>
       <c r="Q5" t="n">
-        <v>202.8671385720814</v>
+        <v>204.7858435031659</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_4</t>
+          <t>model_28_8_20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.999488039843753</v>
+        <v>0.9998093735274778</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5162658630965161</v>
+        <v>0.6766073065615776</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9985927457984028</v>
+        <v>0.9996319417201927</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9987536864989749</v>
+        <v>0.999243411054854</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9986638363840472</v>
+        <v>0.9993440686008763</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003039216642754445</v>
+        <v>0.0001131641087240163</v>
       </c>
       <c r="H6" t="n">
-        <v>0.287165479892573</v>
+        <v>0.1919798726620061</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000844333647070702</v>
+        <v>7.265708941111135e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0004191299459431019</v>
+        <v>0.0005660610912663036</v>
       </c>
       <c r="K6" t="n">
-        <v>0.000631731796506902</v>
+        <v>0.0003193586440137433</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009974939696570933</v>
+        <v>0.003754091074130892</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01743334919845996</v>
+        <v>0.01063786203727123</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000361383639704</v>
+        <v>1.000134559862957</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01817552296584626</v>
+        <v>0.01109073784760805</v>
       </c>
       <c r="P6" t="n">
-        <v>132.1974811461371</v>
+        <v>134.173343006423</v>
       </c>
       <c r="Q6" t="n">
-        <v>202.8922789884927</v>
+        <v>204.8681408487786</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_5</t>
+          <t>model_28_8_19</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9994930857369936</v>
+        <v>0.9998174090122585</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5159460245541323</v>
+        <v>0.6764084874246075</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9985486664202267</v>
+        <v>0.999651378544008</v>
       </c>
       <c r="E7" t="n">
-        <v>0.998703573576383</v>
+        <v>0.999288034744089</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9986180457068443</v>
+        <v>0.9993822959521818</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0003009262040765888</v>
+        <v>0.0001083938978433746</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2873553498676377</v>
+        <v>0.1920979002902511</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008707806827901998</v>
+        <v>6.882013444149064e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0004359827093286743</v>
+        <v>0.0005326747532993958</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0006533814106912928</v>
+        <v>0.000300746583219807</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00974136263576976</v>
+        <v>0.003738323600957716</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0173472246793713</v>
+        <v>0.01041123901576439</v>
       </c>
       <c r="N7" t="n">
-        <v>1.00035782183271</v>
+        <v>1.000128887756053</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01808573194767767</v>
+        <v>0.01085446701490133</v>
       </c>
       <c r="P7" t="n">
-        <v>132.2172909849101</v>
+        <v>134.2594775270021</v>
       </c>
       <c r="Q7" t="n">
-        <v>202.9120888272657</v>
+        <v>204.9542753693577</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_6</t>
+          <t>model_28_8_18</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9994968706127563</v>
+        <v>0.9998254273070809</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5156421374054392</v>
+        <v>0.6761988468643163</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9985060904667536</v>
+        <v>0.9996712747518079</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9986549115611999</v>
+        <v>0.9993335177128189</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9985737233198533</v>
+        <v>0.9994212748817295</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0002986793383257333</v>
+        <v>0.0001036338916644513</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2875357504063432</v>
+        <v>0.1922223519828407</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0008963256838515649</v>
+        <v>6.489249409654698e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0004523475387045937</v>
+        <v>0.0004986455237177855</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0006743368242537179</v>
+        <v>0.0002817685954270401</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009519480907264096</v>
+        <v>0.003721649073413531</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01728234180676141</v>
+        <v>0.01018007326419861</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000355150155702</v>
+        <v>1.000123227783237</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01801808687685471</v>
+        <v>0.01061346005871233</v>
       </c>
       <c r="P8" t="n">
-        <v>132.2322800142551</v>
+        <v>134.3492922840383</v>
       </c>
       <c r="Q8" t="n">
-        <v>202.9270778566107</v>
+        <v>205.0440901263939</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_7</t>
+          <t>model_28_8_17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.999499578079947</v>
+        <v>0.999833398922362</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5153534329606549</v>
+        <v>0.6759776762673699</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9984650481832829</v>
+        <v>0.9996916031016047</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9986077528920356</v>
+        <v>0.9993798428928609</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9985309105196004</v>
+        <v>0.9994609885913081</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0002970720688447783</v>
+        <v>9.890159647770735e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2877071378361498</v>
+        <v>0.1923536484032604</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009209505034809514</v>
+        <v>6.087954612119834e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0004682067991886525</v>
+        <v>0.0004639861725127657</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0006945785123930231</v>
+        <v>0.000262432859316982</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009308508004774901</v>
+        <v>0.003704109263213563</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01723577874204639</v>
+        <v>0.009944928178609806</v>
       </c>
       <c r="N9" t="n">
-        <v>1.00035323900239</v>
+        <v>1.000117600760686</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01796954152607594</v>
+        <v>0.01036830436001258</v>
       </c>
       <c r="P9" t="n">
-        <v>132.2430715851095</v>
+        <v>134.4427703542461</v>
       </c>
       <c r="Q9" t="n">
-        <v>202.9378694274652</v>
+        <v>205.1375681966017</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_8</t>
+          <t>model_28_8_16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9995013316538508</v>
+        <v>0.9998412482529536</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5150792500930093</v>
+        <v>0.6757441974897322</v>
       </c>
       <c r="D10" t="n">
-        <v>0.998425507190736</v>
+        <v>0.9997122784381198</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9985620559341103</v>
+        <v>0.9994267848484445</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9984895691174045</v>
+        <v>0.9995012473865438</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0002960310716250887</v>
+        <v>9.424189476510911e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2878699046304675</v>
+        <v>0.1924922514914241</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0009446745686910621</v>
+        <v>5.679810071920418e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0004835744923808189</v>
+        <v>0.0004288653651386912</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0007141245305359405</v>
+        <v>0.0002428317329289477</v>
       </c>
       <c r="L10" t="n">
-        <v>0.009108036773248302</v>
+        <v>0.003685589998223283</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01720555351115124</v>
+        <v>0.009707826469664007</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000352001185517</v>
+        <v>1.000112060056739</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01793802954452673</v>
+        <v>0.01012110874044875</v>
       </c>
       <c r="P10" t="n">
-        <v>132.250092274886</v>
+        <v>134.5392914650426</v>
       </c>
       <c r="Q10" t="n">
-        <v>202.9448901172416</v>
+        <v>205.2340893073982</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_9</t>
+          <t>model_28_8_15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9995022513384219</v>
+        <v>0.9998489232166543</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5148186337159208</v>
+        <v>0.6754978646072325</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9983874097152314</v>
+        <v>0.9997332906447309</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9985178658201226</v>
+        <v>0.9994742323169118</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9984496800058293</v>
+        <v>0.9995419628798029</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0002954851071353871</v>
+        <v>8.968570477121477e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2880246177699484</v>
+        <v>0.1926384853315024</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0009675325430359982</v>
+        <v>5.265015497737596e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0004984354403458906</v>
+        <v>0.0003933663455577542</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0007329839125873624</v>
+        <v>0.000223008250267565</v>
       </c>
       <c r="L11" t="n">
-        <v>0.008917712048392772</v>
+        <v>0.003666036473174061</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01718968025110959</v>
+        <v>0.009470253680404489</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000351351996408</v>
+        <v>1.000106642435303</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01792148052694293</v>
+        <v>0.009873421985706989</v>
       </c>
       <c r="P11" t="n">
-        <v>132.2537842425064</v>
+        <v>134.6383983373977</v>
       </c>
       <c r="Q11" t="n">
-        <v>202.948582084862</v>
+        <v>205.3331961797533</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_10</t>
+          <t>model_28_8_14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9995024774179178</v>
+        <v>0.9998563430341373</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5145710563355599</v>
+        <v>0.675237804586783</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9983508320206776</v>
+        <v>0.9997545452697388</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9984751787364049</v>
+        <v>0.9995219585160349</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9984112915140136</v>
+        <v>0.9995829423690884</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0002953508965804949</v>
+        <v>8.528098059393984e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2881715903977167</v>
+        <v>0.1927928681936492</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0009894786691935584</v>
+        <v>4.845435427320116e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0005127909256040905</v>
+        <v>0.0003576587866105261</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0007511338087605672</v>
+        <v>0.0002030562337181165</v>
       </c>
       <c r="L12" t="n">
-        <v>0.008736707964768504</v>
+        <v>0.00364544315667434</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01718577599587795</v>
+        <v>0.009234770197137546</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000351192410882</v>
+        <v>1.00010140491708</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01791741005948316</v>
+        <v>0.009627913483039362</v>
       </c>
       <c r="P12" t="n">
-        <v>132.2546928571227</v>
+        <v>134.7391181981821</v>
       </c>
       <c r="Q12" t="n">
-        <v>202.9494906994783</v>
+        <v>205.4339160405377</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_11</t>
+          <t>model_28_8_13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9995020832774727</v>
+        <v>0.9998634295334294</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5143359815438464</v>
+        <v>0.6749632699301404</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9983156417003944</v>
+        <v>0.9997759672288742</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9984339744033678</v>
+        <v>0.9995697743997651</v>
       </c>
       <c r="F13" t="n">
-        <v>0.99837430664502</v>
+        <v>0.9996240233065008</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0002955848753746958</v>
+        <v>8.107412849326502e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.28831114094878</v>
+        <v>0.1929558438251118</v>
       </c>
       <c r="I13" t="n">
-        <v>0.00101059238939606</v>
+        <v>4.422552072793108e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.000526647768095359</v>
+        <v>0.0003218841278637221</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0007686200787457096</v>
+        <v>0.0001830548242958266</v>
       </c>
       <c r="L13" t="n">
-        <v>0.008564835419497506</v>
+        <v>0.003623675363935516</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01719258198685398</v>
+        <v>0.009004117307835622</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000351470627666</v>
+        <v>1.000096402682285</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01792450579558538</v>
+        <v>0.009387441222722552</v>
       </c>
       <c r="P13" t="n">
-        <v>132.2531090720988</v>
+        <v>134.8402933104359</v>
       </c>
       <c r="Q13" t="n">
-        <v>202.9479069144544</v>
+        <v>205.5350911527915</v>
       </c>
     </row>
     <row r="14">
@@ -1177,712 +1177,712 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9995011774921222</v>
+        <v>0.9998700742456249</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5141125200685062</v>
+        <v>0.6746735745704541</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9982818780359803</v>
+        <v>0.9997974408322695</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9983943075161523</v>
+        <v>0.9996173622278778</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9983387753878301</v>
+        <v>0.9996649391768405</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0002961225886865957</v>
+        <v>7.712954029741353e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2884437973335751</v>
+        <v>0.1931278195048096</v>
       </c>
       <c r="I14" t="n">
-        <v>0.001030850135211178</v>
+        <v>3.998649227112203e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0005399875740757042</v>
+        <v>0.0002862800946760076</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0007854190879903397</v>
+        <v>0.0001631337824188657</v>
       </c>
       <c r="L14" t="n">
-        <v>0.008401517889676859</v>
+        <v>0.003600846297394905</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01720821282663007</v>
+        <v>0.008782342529041641</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000352110005561</v>
+        <v>1.000091712297206</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01794080207257104</v>
+        <v>0.009156225032458229</v>
       </c>
       <c r="P14" t="n">
-        <v>132.2494740768176</v>
+        <v>134.9400484162742</v>
       </c>
       <c r="Q14" t="n">
-        <v>202.9442719191733</v>
+        <v>205.6348462586298</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_13</t>
+          <t>model_28_8_11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9994998264888113</v>
+        <v>0.9998761732931538</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5139002203996965</v>
+        <v>0.6743676605507949</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9982494589457004</v>
+        <v>0.9998188894397723</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9983560593521251</v>
+        <v>0.9996644538469587</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9983046018280113</v>
+        <v>0.9997054709150249</v>
       </c>
       <c r="G15" t="n">
-        <v>0.000296924602612238</v>
+        <v>7.350888221914056e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2885698275878487</v>
+        <v>0.1933094232816769</v>
       </c>
       <c r="I15" t="n">
-        <v>0.001050301154579079</v>
+        <v>3.575239816544757e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0005528502694633014</v>
+        <v>0.0002510473127837526</v>
       </c>
       <c r="K15" t="n">
-        <v>0.000801576184381566</v>
+        <v>0.0001433997660821046</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00824628795542646</v>
+        <v>0.003576664087570767</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01723150030067719</v>
+        <v>0.008573732105631745</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000353063654957</v>
+        <v>1.000087407087185</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01796508094260005</v>
+        <v>0.008938733631440666</v>
       </c>
       <c r="P15" t="n">
-        <v>132.2440646292975</v>
+        <v>135.0362086250558</v>
       </c>
       <c r="Q15" t="n">
-        <v>202.9388624716532</v>
+        <v>205.7310064674114</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_14</t>
+          <t>model_28_8_10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9994981053880665</v>
+        <v>0.9998815944981755</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5136985741384614</v>
+        <v>0.6740445690646275</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9982183675210569</v>
+        <v>0.9998401505095732</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9983192846070396</v>
+        <v>0.99971066952531</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9982717957006768</v>
+        <v>0.9997452902431294</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0002979463223620916</v>
+        <v>7.02906207343705e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2886895335191828</v>
+        <v>0.1935012243446914</v>
       </c>
       <c r="I16" t="n">
-        <v>0.001068955592371518</v>
+        <v>3.155532521735554e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.000565217460308237</v>
+        <v>0.0002164698880288699</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0008170867652041409</v>
+        <v>0.0001240126066231127</v>
       </c>
       <c r="L16" t="n">
-        <v>0.008098835838245914</v>
+        <v>0.003551284823979433</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01726112170057588</v>
+        <v>0.00838395018677774</v>
       </c>
       <c r="N16" t="n">
-        <v>1.0003542785496</v>
+        <v>1.000083580354229</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01799596338681719</v>
+        <v>0.008740872303398315</v>
       </c>
       <c r="P16" t="n">
-        <v>132.2371944279705</v>
+        <v>135.1257443715347</v>
       </c>
       <c r="Q16" t="n">
-        <v>202.9319922703262</v>
+        <v>205.8205422138903</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_15</t>
+          <t>model_28_8_9</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9994960708576398</v>
+        <v>0.999886201113759</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5135070711082965</v>
+        <v>0.6737033506298493</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9981885726404752</v>
+        <v>0.9998611047407979</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9982838933777208</v>
+        <v>0.999755613208401</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9982403054914173</v>
+        <v>0.9997840703848692</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0002991541075104815</v>
+        <v>6.755593472855495e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2888032179903888</v>
+        <v>0.1937037863474446</v>
       </c>
       <c r="I17" t="n">
-        <v>0.001086832121115953</v>
+        <v>2.741882419248833e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0005771193806669726</v>
+        <v>0.0001828441385922034</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0008319751862256209</v>
+        <v>0.000105131404263818</v>
       </c>
       <c r="L17" t="n">
-        <v>0.007958666718681453</v>
+        <v>0.00352449966084003</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01729607202547681</v>
+        <v>0.008219241736836492</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000355714688725</v>
+        <v>1.000080328625582</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0180324016194063</v>
+        <v>0.008569151873749573</v>
       </c>
       <c r="P17" t="n">
-        <v>132.229103415235</v>
+        <v>135.2051092811837</v>
       </c>
       <c r="Q17" t="n">
-        <v>202.9239012575906</v>
+        <v>205.8999071235394</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_16</t>
+          <t>model_28_8_8</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9994937857409816</v>
+        <v>0.9998898223936098</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5133251412150603</v>
+        <v>0.6733430540409471</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9981600508091076</v>
+        <v>0.9998815473758582</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9982499120714725</v>
+        <v>0.9997987974830947</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9982101215846652</v>
+        <v>0.9998213949133554</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0003005106514706923</v>
+        <v>6.540618657798237e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.288911219433976</v>
+        <v>0.1939176739666192</v>
       </c>
       <c r="I18" t="n">
-        <v>0.001103944837405846</v>
+        <v>2.338331556556669e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0005885471498752769</v>
+        <v>0.0001505347348988117</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0008462459936405617</v>
+        <v>8.695890814342104e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.007825605173559437</v>
+        <v>0.003496307367256334</v>
       </c>
       <c r="M18" t="n">
-        <v>0.01733524304619616</v>
+        <v>0.008087409138777533</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000357327712248</v>
+        <v>1.00007777242804</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01807324023157286</v>
+        <v>0.008431706889060146</v>
       </c>
       <c r="P18" t="n">
-        <v>132.2200547175825</v>
+        <v>135.2697874159629</v>
       </c>
       <c r="Q18" t="n">
-        <v>202.9148525599382</v>
+        <v>205.9645852583185</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_17</t>
+          <t>model_28_8_7</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9994912914942276</v>
+        <v>0.9998922792724956</v>
       </c>
       <c r="C19" t="n">
-        <v>0.513152254294567</v>
+        <v>0.6729623993829819</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9981327197117742</v>
+        <v>0.9999013144435041</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9982173248919132</v>
+        <v>0.9998396869839784</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9981811907414578</v>
+        <v>0.9998568189986983</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0003019913440897732</v>
+        <v>6.394767713976276e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2890138525783069</v>
+        <v>0.1941436470150123</v>
       </c>
       <c r="I19" t="n">
-        <v>0.001120343129245219</v>
+        <v>1.948116832385537e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0005995060801892901</v>
+        <v>0.0001199422240776658</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0008599243585770339</v>
+        <v>6.97116962007606e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>0.007699137664375148</v>
+        <v>0.003466595477029588</v>
       </c>
       <c r="M19" t="n">
-        <v>0.017377898149367</v>
+        <v>0.007996729152582496</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000359088357016</v>
+        <v>1.000076038160591</v>
       </c>
       <c r="O19" t="n">
-        <v>0.01811771125079392</v>
+        <v>0.008337166468119337</v>
       </c>
       <c r="P19" t="n">
-        <v>132.2102244059091</v>
+        <v>135.3148907073355</v>
       </c>
       <c r="Q19" t="n">
-        <v>202.9050222482647</v>
+        <v>206.0096885496911</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_18</t>
+          <t>model_28_8_6</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9994886234462771</v>
+        <v>0.9998933561243351</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5129879338124721</v>
+        <v>0.6725602184319166</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9981065491228068</v>
+        <v>0.9999201707304425</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9981859930117993</v>
+        <v>0.9998776357801631</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9981534428794115</v>
+        <v>0.9998897992258089</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0003035752126067935</v>
+        <v>6.330841137029011e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2891114003147536</v>
+        <v>0.1943823990008771</v>
       </c>
       <c r="I20" t="n">
-        <v>0.001136045131629554</v>
+        <v>1.575881509552859e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0006100428586223402</v>
+        <v>9.154987560578312e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0008730434156523948</v>
+        <v>5.365434535065586e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.007578993914595988</v>
+        <v>0.003435217853962784</v>
       </c>
       <c r="M20" t="n">
-        <v>0.01742340990181869</v>
+        <v>0.007956658304231125</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000360971684981</v>
+        <v>1.000075278029881</v>
       </c>
       <c r="O20" t="n">
-        <v>0.01816516053276979</v>
+        <v>0.008295389720795555</v>
       </c>
       <c r="P20" t="n">
-        <v>132.1997623213622</v>
+        <v>135.3349847131896</v>
       </c>
       <c r="Q20" t="n">
-        <v>202.8945601637178</v>
+        <v>206.0297825555452</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_19</t>
+          <t>model_28_8_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9994858360626527</v>
+        <v>0.9998928164204585</v>
       </c>
       <c r="C21" t="n">
-        <v>0.512831885660638</v>
+        <v>0.6721353210538961</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9980815319444859</v>
+        <v>0.9999378427807407</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9981560160168504</v>
+        <v>0.9999119520741587</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9981269073268039</v>
+        <v>0.9999197483821362</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0003052299239349358</v>
+        <v>6.36288029053923e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2892040372386115</v>
+        <v>0.1946346364390811</v>
       </c>
       <c r="I21" t="n">
-        <v>0.001151055103095391</v>
+        <v>1.227023785372985e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0006201239949192035</v>
+        <v>6.587527521413734e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0008855892985967146</v>
+        <v>3.90727565339336e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.007464793680208735</v>
+        <v>0.00340221701794327</v>
       </c>
       <c r="M21" t="n">
-        <v>0.01747083065955754</v>
+        <v>0.007976766444204838</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000362939249892</v>
+        <v>1.000075658997323</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01821460009034009</v>
+        <v>0.008316353905917537</v>
       </c>
       <c r="P21" t="n">
-        <v>132.1888904327826</v>
+        <v>135.3248886285292</v>
       </c>
       <c r="Q21" t="n">
-        <v>202.8836882751382</v>
+        <v>206.0196864708848</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_20</t>
+          <t>model_28_8_4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9994829461879239</v>
+        <v>0.9998903925613104</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5126836269240298</v>
+        <v>0.6716862844098108</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9980576124246263</v>
+        <v>0.9999540469072248</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9981272257818088</v>
+        <v>0.9999418076507456</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9981014910163696</v>
+        <v>0.9999459724841094</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0003069454784100497</v>
+        <v>6.506771040098051e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2892920500291061</v>
+        <v>0.1949012039883832</v>
       </c>
       <c r="I22" t="n">
-        <v>0.001165406494206013</v>
+        <v>9.071438284812269e-06</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0006298060288912263</v>
+        <v>4.353807299679849e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0008976060091698341</v>
+        <v>2.630481516406774e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.007356295185185379</v>
+        <v>0.00336749224403703</v>
       </c>
       <c r="M22" t="n">
-        <v>0.01751985954310278</v>
+        <v>0.008066455876094563</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000364979161465</v>
+        <v>1.000077369956722</v>
       </c>
       <c r="O22" t="n">
-        <v>0.01826571623496163</v>
+        <v>0.008409861602605527</v>
       </c>
       <c r="P22" t="n">
-        <v>132.1776808418089</v>
+        <v>135.2801642635667</v>
       </c>
       <c r="Q22" t="n">
-        <v>202.8724786841645</v>
+        <v>205.9749621059224</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_21</t>
+          <t>model_28_8_3</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9994799920964652</v>
+        <v>0.9998857819097079</v>
       </c>
       <c r="C23" t="n">
-        <v>0.512542890798262</v>
+        <v>0.6712116622094573</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9980347609205269</v>
+        <v>0.9999684463880661</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9980996784400561</v>
+        <v>0.9999663017879621</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9980771944028111</v>
+        <v>0.9999677115100495</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0003086991547100769</v>
+        <v>6.780479236196982e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.289375597072846</v>
+        <v>0.1951829602291245</v>
       </c>
       <c r="I23" t="n">
-        <v>0.001179117090184637</v>
+        <v>6.22888745968134e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0006390700831200993</v>
+        <v>2.521216679454633e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.000909093332390644</v>
+        <v>1.572055916459972e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.00725322504150692</v>
+        <v>0.003330994440443935</v>
       </c>
       <c r="M23" t="n">
-        <v>0.01756983650208723</v>
+        <v>0.008234366542847715</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000367064402495</v>
+        <v>1.000080624534324</v>
       </c>
       <c r="O23" t="n">
-        <v>0.01831782081655662</v>
+        <v>0.008584920574065359</v>
       </c>
       <c r="P23" t="n">
-        <v>132.1662867293689</v>
+        <v>135.1977553634221</v>
       </c>
       <c r="Q23" t="n">
-        <v>202.8610845717246</v>
+        <v>205.8925532057777</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_22</t>
+          <t>model_28_8_2</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9994769870340953</v>
+        <v>0.999878649728315</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5124090665920884</v>
+        <v>0.6707100832030308</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9980129059281281</v>
+        <v>0.9999806652532044</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9980732623530502</v>
+        <v>0.9999843783343363</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9980539318706683</v>
+        <v>0.9999840775886814</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0003104830895447709</v>
+        <v>7.203876333099773e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2894550409025353</v>
+        <v>0.1954807191944242</v>
       </c>
       <c r="I24" t="n">
-        <v>0.001192229792507958</v>
+        <v>3.816804304482461e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0006479537011742512</v>
+        <v>1.168774295439668e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0009200917468411046</v>
+        <v>7.75227362943957e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>0.00715518692818114</v>
+        <v>0.003318285427878638</v>
       </c>
       <c r="M24" t="n">
-        <v>0.01762053034232429</v>
+        <v>0.008487565218070358</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000369185622991</v>
+        <v>1.000085659015307</v>
       </c>
       <c r="O24" t="n">
-        <v>0.01837067279852328</v>
+        <v>0.008848898441085743</v>
       </c>
       <c r="P24" t="n">
-        <v>132.1547622401749</v>
+        <v>135.0766124084506</v>
       </c>
       <c r="Q24" t="n">
-        <v>202.8495600825306</v>
+        <v>205.7714102508063</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_23</t>
+          <t>model_28_8_1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9994739583531466</v>
+        <v>0.9998686153381234</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5122820187337136</v>
+        <v>0.670179828329089</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9979920251083919</v>
+        <v>0.9999902763430499</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9980480157759122</v>
+        <v>0.9999948606281961</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9980317039304418</v>
+        <v>0.9999940799727234</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0003122810453881383</v>
+        <v>7.79956108118105e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2895304619994483</v>
+        <v>0.195795501393414</v>
       </c>
       <c r="I25" t="n">
-        <v>0.00120475800429917</v>
+        <v>1.919512890170193e-06</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0006564440180186042</v>
+        <v>3.8451505673962e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0009306010111588872</v>
+        <v>2.882331728783196e-06</v>
       </c>
       <c r="L25" t="n">
-        <v>0.007062183604217948</v>
+        <v>0.003347086942282692</v>
       </c>
       <c r="M25" t="n">
-        <v>0.01767147547286695</v>
+        <v>0.008831512373982754</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000371323515426</v>
+        <v>1.000092742114266</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0184237867687441</v>
+        <v>0.009207488139494097</v>
       </c>
       <c r="P25" t="n">
-        <v>132.1432139782381</v>
+        <v>134.9177160090029</v>
       </c>
       <c r="Q25" t="n">
-        <v>202.8380118205937</v>
+        <v>205.6125138513585</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_28_8_24</t>
+          <t>model_28_8_0</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9994709205115875</v>
+        <v>0.999855242807037</v>
       </c>
       <c r="C26" t="n">
-        <v>0.512161261231026</v>
+        <v>0.669619104370645</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9979720796829555</v>
+        <v>0.9999967989419959</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9980238291287513</v>
+        <v>0.9999964141962188</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9980104464674068</v>
+        <v>0.9999965961380045</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0003140844393655171</v>
+        <v>8.593412292801769e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2896021488694962</v>
+        <v>0.1961283713571601</v>
       </c>
       <c r="I26" t="n">
-        <v>0.001216724992055842</v>
+        <v>6.319095925159964e-07</v>
       </c>
       <c r="J26" t="n">
-        <v>0.000664577884905799</v>
+        <v>2.682809489231687e-06</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0009406514384808205</v>
+        <v>1.657265916421583e-06</v>
       </c>
       <c r="L26" t="n">
-        <v>0.006973808076983381</v>
+        <v>0.003384604428750222</v>
       </c>
       <c r="M26" t="n">
-        <v>0.01772242758104874</v>
+        <v>0.009270065961362825</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000373467874174</v>
+        <v>1.000102181547974</v>
       </c>
       <c r="O26" t="n">
-        <v>0.01847690801365659</v>
+        <v>0.009664711861020015</v>
       </c>
       <c r="P26" t="n">
-        <v>132.1316973860608</v>
+        <v>134.7238591354263</v>
       </c>
       <c r="Q26" t="n">
-        <v>202.8264952284165</v>
+        <v>205.4186569777819</v>
       </c>
     </row>
   </sheetData>
